--- a/review/etnografiya/may-december/accepted/february/february.xlsx
+++ b/review/etnografiya/may-december/accepted/february/february.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Одна деревянная доска — а узором можно покрыть целый сарафан. Как?</t>
+          <t xml:space="preserve">Одна резная доска оставляет узор снова и снова. Набойка превращает небольшой деревянный рисунок в ткань для целого наряда.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Десятки деревянных палочек — как не запутать нити?</t>
+          <t xml:space="preserve">Десятки коклюшек движутся в руках кружевницы. Каждая держит свою нить, а порядок перекрещиваний превращает их в лёгкий ажур.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему эту одежду узнают по клетке — и почему она не похожа на сарафан?</t>
+          <t xml:space="preserve">Клетчатая понёва из Парахина устроена иначе, чем сарафан. За рисунком ткани открывается крой конкретной вещи и мастерство местной традиции.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем в женском головном уборе твёрдые рога?</t>
+          <t xml:space="preserve">Под нарядным верхом кички скрыты твёрдые рога. Необычный силуэт создаётся из нескольких частей и связан с убором замужней женщины.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как шить двумя руками, если ткань всё время приходится держать?</t>
+          <t xml:space="preserve">Деревянная швейка держит край ткани, пока руки ведут шов. Небольшая помощница берёт на себя ту работу, для которой не хватает третьей руки.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему колыбель висит, а не стоит на полу?</t>
+          <t xml:space="preserve">Колыбель висит над полом. Подвес меняет движение детской постели — устройство домашней вещи становится частью заботы о ребёнке.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ни мотора, ни батарейки. Кто заставляет кузнецов стучать молотками?</t>
+          <t xml:space="preserve">Ни мотора, ни батарейки — кузнецы стучат молотками. Движение деревянных планок оживляет игрушку, вырезанную мастером.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крана нет. Как вымыть руки и не вылить сразу всю воду?</t>
+          <t xml:space="preserve">У рукомойника нет крана, но воду можно выпускать понемногу. Простая форма помогает вымыть руки, не опорожняя весь запас за один раз.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему два ведра могли быть удобнее одного?</t>
+          <t xml:space="preserve">Два ведра висят по сторонам коромысла. Нагрузка распределяется между ними — знакомый предмет превращает тяжёлую ношу в продуманную систему.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дощечки прижаты обручами — почему эта кадушка подходит для теста?</t>
+          <t xml:space="preserve">Дощечки квашни стянуты обручами. Ёмкость собирается из отдельных частей и служит месту, где замешивают и оставляют подниматься тесто.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">У чаши широкий бок и слив. Как из неё угощали целую компанию?</t>
+          <t xml:space="preserve">Широкая чаша и носик помогают разливать угощение. Форма сосуда хранит порядок общей трапезы — вещь сделана для встречи людей.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Этой кадушкой пользовалась одна семья больше полувека. Что происходило внутри?</t>
+          <t xml:space="preserve">Одной маслобойкой семья пользовалась больше полувека. За деревянными стенками привычным движением превращали сливки в масло.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар положили на чашу. Что должно появиться на другой стороне?</t>
+          <t xml:space="preserve">Товар лежит на одной чаше, гири — на другой. Равновесие делает меру видимой обоим участникам торговли, ещё до появления цифры на экране.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Урожай собран. Почему за него всё ещё тревожились зимой?</t>
+          <t xml:space="preserve">Урожай уже собран, а забота о нём продолжается зимой. Хранение запасов требует труда не меньше, чем праздничная благодарность за плоды.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как церковная встреча стала в народном календаре встречей зимы с весной?</t>
+          <t xml:space="preserve">Сретение означает встречу, а народный календарь связывает день со встречей зимы и весны. Церковный смысл и сезонный образ живут рядом.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем вырезать рыб на доске, с которой получается огромный пряник?</t>
+          <t xml:space="preserve">Рыбы вырезаны в дереве, чтобы появиться на прянике. Доска хранит рисунок большого угощения — съедобный рельеф начинается с работы резчика.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ленты, иголки, пуговицы — как целая лавка помещалась на плечах?</t>
+          <t xml:space="preserve">Ленты, иголки и пуговицы умещаются в переносной лавке. Коробейник несёт товар на себе и связывает торговлю с дорогой между поселениями.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему на столе столько мучного и молочного?</t>
+          <t xml:space="preserve">На столе мучное и молочное. Масленичное угощение принадлежит определённому месту в годовом круге — сам праздник меняет дату каждый год.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как катание с горки связывали с будущим урожаем?</t>
+          <t xml:space="preserve">Катание с горки связывали с будущим урожаем. Зимняя забава хранит народное пожелание благополучия, а не способ управлять полем.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто кому приходится роднёй — и к кому идут молодые супруги?</t>
+          <t xml:space="preserve">Молодые супруги входят в новую сеть родства. Праздничные визиты делают эту связь зримой: у каждого родственника своё место во встрече.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему уличная кукла могла говорить со зрителями так бойко?</t>
+          <t xml:space="preserve">Маленькая уличная кукла бойко отвечает зрителям. За голосом и движением Петрушки стоит артист, умеющий превратить толпу в собеседника.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лошадей ещё не видно, а об их приближении уже знают. Откуда идёт звон?</t>
+          <t xml:space="preserve">Лошадей ещё не видно, а звон уже слышен. Поддужный колокольчик делает приближение упряжки слышимым раньше, чем она покажется на дороге.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем крестьянин оставил своё имя на дуге?</t>
+          <t xml:space="preserve">На расписной дуге осталось имя хозяина. Рабочая часть упряжи хранит личный след человека — надпись пережила привычную дорогу.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему благополучию скота посвящали особый день?</t>
+          <t xml:space="preserve">Благополучию скота посвящали особый день. Народный календарь сохраняет прямую связь семейной жизни с животными, от которых зависел достаток.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Озеро подо льдом — зачем сейчас работать над летними снастями?</t>
+          <t xml:space="preserve">Озеро подо льдом, а руки готовят снасти к открытой воде. Рыбацкий год продолжается зимой: будущий выход начинается за домашней работой.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему местным рыбакам зимой мешала дешёвая привозная рыба?</t>
+          <t xml:space="preserve">Привозная рыба меняет жизнь местного промысла. За ценой на зимнем рынке стоят дорога, сезон и труд людей, ловивших рядом с домом.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что мастер называет кокорой — и где её искать в лодке?</t>
+          <t xml:space="preserve">Кокора использует естественный изгиб дерева. В лодке природная форма становится конструктивной деталью — мастерство начинается с выбора заготовки.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ремесло становится личным открытием человека нашего времени?</t>
+          <t xml:space="preserve">Человек нашего времени осваивает старое ремесло руками. Между музейной вещью и личным опытом появляется связь через освоенное движение.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
